--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J38-ModeAcces-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J38-ModeAcces-CISIS.xlsx
@@ -30,13 +30,13 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:1.2.250.1.213.1.1.4.248</t>
+    <t>OID:1.2.250.1.213.1.1.4.336</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>20200424120000</t>
+    <t>20241122120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2020-04-24T12:00:00+01:00</t>
+    <t>2024-11-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
